--- a/KatalonData/EmailTextToPay/Manage_EmailText_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText_Prod.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="166">
   <si>
     <t>Result</t>
   </si>
@@ -524,6 +524,117 @@
   </si>
   <si>
     <t>Thu Jul 09 11:41:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:20:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:22:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:23:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:23:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:24:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:24:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:25:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:25:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:26:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:27:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:27:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:28:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:28:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:29:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:30:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:31:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:31:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:32:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:32:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:33:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:34:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:35:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:36:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:37:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:38:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:39:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:41:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:42:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:42:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:43:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:44:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:45:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:46:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:47:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:48:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:50:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 01:50:12 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1176,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>54</v>
@@ -1082,7 +1193,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>54</v>
@@ -1148,7 +1259,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -1204,7 +1315,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1260,7 +1371,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1316,7 +1427,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1379,7 +1490,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>32</v>
@@ -1400,7 +1511,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>33</v>
@@ -1427,7 +1538,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -1450,7 +1561,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -1473,7 +1584,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>30</v>
@@ -1496,7 +1607,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>31</v>
@@ -1519,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>43</v>
@@ -1542,7 +1653,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>44</v>
@@ -1565,7 +1676,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>45</v>
@@ -1631,7 +1742,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>36</v>
@@ -1657,7 +1768,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>39</v>
@@ -1677,7 +1788,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>40</v>
@@ -1697,7 +1808,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>41</v>
@@ -1720,7 +1831,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>21</v>
@@ -1743,7 +1854,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>22</v>
@@ -1766,7 +1877,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>23</v>
@@ -1793,7 +1904,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>38</v>
@@ -1871,7 +1982,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>48</v>
@@ -1948,7 +2059,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>49</v>
@@ -2025,7 +2136,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>50</v>
@@ -2102,7 +2213,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>10</v>
@@ -2179,7 +2290,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>11</v>
@@ -2256,7 +2367,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>12</v>
@@ -2313,7 +2424,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>13</v>
@@ -2382,7 +2493,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>51</v>
@@ -2451,7 +2562,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>52</v>
@@ -2516,7 +2627,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -2572,7 +2683,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
